--- a/docs_for_guenther/Budget_plan_BiH.xlsx
+++ b/docs_for_guenther/Budget_plan_BiH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raidl\proj\AT-BiH-Proposals-27-29\docs_for_guenther\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE9DBB6-32A7-4A80-A7B8-B6BCEBE1ECC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EAF6D7-9678-4359-92B1-95C0A715AC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="2268" windowWidth="21252" windowHeight="21288" xr2:uid="{973348A5-EF7E-40B5-BD40-7EB5CB1B7215}"/>
+    <workbookView xWindow="192" yWindow="1836" windowWidth="21252" windowHeight="21288" xr2:uid="{973348A5-EF7E-40B5-BD40-7EB5CB1B7215}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,40 +36,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
   <si>
     <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>3.</t>
-  </si>
-  <si>
-    <t>4.</t>
-  </si>
-  <si>
-    <t>b</t>
   </si>
   <si>
     <t>Name of Austrian 
 team member</t>
   </si>
   <si>
-    <t>Example (NOT to fill in the line)</t>
-  </si>
-  <si>
     <t>Sum</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>(Additional) Accommodation Costs Dr. Muster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Additional) Material Costs </t>
   </si>
   <si>
     <t>Type of material</t>
@@ -225,6 +201,9 @@
   </si>
   <si>
     <t>6 working days</t>
+  </si>
+  <si>
+    <t>3 working days</t>
   </si>
 </sst>
 </file>
@@ -870,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -880,12 +859,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -899,7 +872,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -914,25 +886,11 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -940,20 +898,13 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -978,18 +929,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="8" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1015,9 +957,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1063,47 +1002,25 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1126,6 +1043,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1138,39 +1058,30 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1554,7 +1465,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.88671875" customWidth="1"/>
@@ -1563,619 +1474,503 @@
     <col min="4" max="4" width="18.109375" customWidth="1"/>
     <col min="5" max="5" width="22.6640625" customWidth="1"/>
     <col min="6" max="6" width="28.33203125" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" style="53" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="33" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="3" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="111"/>
+      <c r="A1" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="79"/>
       <c r="J1"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="113"/>
-      <c r="K2" s="22"/>
+      <c r="A2" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="82"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="104" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="106"/>
+      <c r="A3" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="74"/>
+      <c r="A4" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="74"/>
+      <c r="A5" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="107"/>
-      <c r="B6" s="107"/>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="75" t="s">
+      <c r="A7" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="B7" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>19</v>
+      <c r="C7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
     </row>
     <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="83">
+      <c r="A8" s="59">
         <v>1</v>
       </c>
-      <c r="B8" s="78">
+      <c r="B8" s="54">
         <v>2027</v>
       </c>
-      <c r="C8" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="67">
+      <c r="C8" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="44">
+        <v>300</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="45">
+        <v>360</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="39">
+        <f t="shared" ref="H8:H14" si="0">SUM(D8+F8)</f>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="59">
+        <v>2</v>
+      </c>
+      <c r="B9" s="54">
+        <v>2027</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="44">
         <v>600</v>
       </c>
-      <c r="E8" s="65" t="s">
+      <c r="E9" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="45">
+        <v>720</v>
+      </c>
+      <c r="G9" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="68">
-        <v>720</v>
-      </c>
-      <c r="G8" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="62">
-        <f t="shared" ref="H8:H14" si="0">SUM(D8+F8)</f>
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="83">
-        <v>2</v>
-      </c>
-      <c r="B9" s="78">
-        <v>2027</v>
-      </c>
-      <c r="C9" s="79" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="67">
-        <v>600</v>
-      </c>
-      <c r="E9" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="68">
-        <v>720</v>
-      </c>
-      <c r="G9" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="62">
+      <c r="H9" s="39">
         <f t="shared" si="0"/>
         <v>1320</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="83">
+      <c r="A10" s="59">
         <v>3</v>
       </c>
-      <c r="B10" s="78">
+      <c r="B10" s="54">
         <v>2027</v>
       </c>
-      <c r="C10" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="67">
+      <c r="C10" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="44">
+        <v>300</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="45">
+        <v>360</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="39">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="59">
+        <v>4</v>
+      </c>
+      <c r="B11" s="54">
+        <v>2027</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="44">
         <v>600</v>
       </c>
-      <c r="E10" s="65" t="s">
+      <c r="E11" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="45">
+        <v>720</v>
+      </c>
+      <c r="G11" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="68">
-        <v>720</v>
-      </c>
-      <c r="G10" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="62">
+      <c r="H11" s="39">
         <f t="shared" si="0"/>
         <v>1320</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="83">
-        <v>4</v>
-      </c>
-      <c r="B11" s="78">
-        <v>2027</v>
-      </c>
-      <c r="C11" s="79" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="67">
+    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="59">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58">
+        <v>2028</v>
+      </c>
+      <c r="C12" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="44">
+        <v>300</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="63">
+        <v>360</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="39">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="59">
+        <v>6</v>
+      </c>
+      <c r="B13" s="58">
+        <v>2028</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="44">
+        <v>300</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="63">
+        <v>360</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="39">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="59">
+        <v>8</v>
+      </c>
+      <c r="B14" s="56">
+        <v>2028</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="44">
         <v>600</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E14" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="63">
+        <v>720</v>
+      </c>
+      <c r="G14" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="68">
-        <v>720</v>
-      </c>
-      <c r="G11" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="62">
+      <c r="H14" s="39">
         <f t="shared" si="0"/>
         <v>1320</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="83">
-        <v>5</v>
-      </c>
-      <c r="B12" s="82">
-        <v>2028</v>
-      </c>
-      <c r="C12" s="86" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="67">
-        <v>600</v>
-      </c>
-      <c r="E12" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="87">
-        <v>720</v>
-      </c>
-      <c r="G12" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="62">
-        <f t="shared" si="0"/>
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="83">
+    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="90"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="16">
+        <f>SUM(H8:H14)</f>
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="14"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="82">
-        <v>2028</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="67">
-        <v>600</v>
-      </c>
-      <c r="E13" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="87">
-        <v>720</v>
-      </c>
-      <c r="G13" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="62">
-        <f t="shared" si="0"/>
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="83">
+      <c r="C17" s="83" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="53"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="17">
+        <f>SUM(0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="92"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+    </row>
+    <row r="21" spans="1:8" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="80">
-        <v>2028</v>
-      </c>
-      <c r="C14" s="79" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="67">
-        <v>600</v>
-      </c>
-      <c r="E14" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="87">
-        <v>720</v>
-      </c>
-      <c r="G14" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="62">
-        <f t="shared" si="0"/>
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="92"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="23">
-        <f>SUM(H8:H14)</f>
-        <v>9240</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="21"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="20"/>
-    </row>
-    <row r="17" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="75" t="s">
+      <c r="B23" s="87"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="40"/>
+    </row>
+    <row r="24" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="114" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="77"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="B24" s="27"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="41">
+        <f>SUM(H15+H19)</f>
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+    </row>
+    <row r="27" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" ht="159" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="69"/>
+    </row>
+    <row r="29" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="18"/>
-    </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="24">
-        <f>SUM(H19:H22)</f>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="21">
+        <f>SUM(H29:H29)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="94"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-    </row>
-    <row r="25" spans="1:8" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="89"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="63"/>
-    </row>
-    <row r="28" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="64">
-        <f>SUM(H15+H23)</f>
-        <v>9240</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="119" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="119"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-    </row>
-    <row r="31" spans="1:8" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" ht="159" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="120" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="121"/>
-      <c r="C32" s="121"/>
-      <c r="D32" s="121"/>
-      <c r="E32" s="121"/>
-      <c r="F32" s="121"/>
-      <c r="G32" s="121"/>
-      <c r="H32" s="122"/>
-    </row>
-    <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="124" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="125"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="57"/>
-      <c r="H33" s="27">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="123" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="123"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" s="58"/>
-      <c r="H34" s="29">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="47"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="32"/>
-    </row>
-    <row r="36" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36" s="47"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="127"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="32"/>
-    </row>
-    <row r="37" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="128"/>
-      <c r="D37" s="129"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="33"/>
-    </row>
-    <row r="38" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="117" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="118"/>
-      <c r="C38" s="118"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="118"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="36">
-        <f>SUM(H35:H37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="85" t="s">
-        <v>24</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
+  <mergeCells count="14">
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C17:G17"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="C29:D29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
